--- a/artfynd/A 62949-2021 artfynd.xlsx
+++ b/artfynd/A 62949-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62949-2021 artfynd.xlsx
+++ b/artfynd/A 62949-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1867084</v>
+        <v>97363629</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527775.316522166</v>
+        <v>528106</v>
       </c>
       <c r="R2" t="n">
-        <v>7032329.566041535</v>
+        <v>7032607</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6476800</v>
+        <v>97363630</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,23 +787,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blekspindling agg.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiostramineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527818.9706983247</v>
+        <v>527971</v>
       </c>
       <c r="R3" t="n">
-        <v>7032260.96627489</v>
+        <v>7032344</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,53 +857,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>206855</v>
+        <v>97363709</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,13 +908,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527766.6501423704</v>
+        <v>528047</v>
       </c>
       <c r="R4" t="n">
-        <v>7032294.553498173</v>
+        <v>7032609</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,53 +958,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>486941</v>
+        <v>97363713</v>
       </c>
       <c r="B5" t="n">
-        <v>92505</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2412</v>
+        <v>445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1009,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527817.0409522905</v>
+        <v>527972</v>
       </c>
       <c r="R5" t="n">
-        <v>7032328.136991144</v>
+        <v>7032608</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1059,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1979995</v>
+        <v>97363737</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,13 +1110,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527820.3317562153</v>
+        <v>527973</v>
       </c>
       <c r="R6" t="n">
-        <v>7032259.18642661</v>
+        <v>7032342</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,69 +1160,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1979994</v>
+        <v>62326102</v>
       </c>
       <c r="B7" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundflyberget, Jmt</t>
+          <t>Skyttmon / V /, väg 344,, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527749.8019123212</v>
+        <v>528060</v>
       </c>
       <c r="R7" t="n">
-        <v>7032272.011381323</v>
+        <v>7032213</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1242,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 små bestånd. 3 små bestånd i södra vägdiket varav ett halshugget vid tidig vägkantsslåtter. Flera spridda växtplatser har funnits längs vägen i anslutning till kommungränsen. Oklart hur många som finns kvar. En del kan vara bortdikade. Södra sidan väg 344, väster om Skyttmon, 200 m väster om väg 772, söder om Grundflyberget.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,57 +1263,57 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Vägkant, vägdike,</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Åsa Stenman</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97363739</v>
+        <v>97363705</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527888.074454352</v>
+        <v>528075</v>
       </c>
       <c r="R8" t="n">
-        <v>7032514.633670448</v>
+        <v>7032232</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,21 +1356,11 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1467,11 +1369,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1492,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97363717</v>
+        <v>206855</v>
       </c>
       <c r="B9" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3739</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527985.1474016994</v>
+        <v>527767</v>
       </c>
       <c r="R9" t="n">
-        <v>7032338.113717796</v>
+        <v>7032295</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,53 +1474,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97363722</v>
+        <v>206856</v>
       </c>
       <c r="B10" t="n">
-        <v>86136</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4379</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,13 +1525,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527980.1866834515</v>
+        <v>527764</v>
       </c>
       <c r="R10" t="n">
-        <v>7032341.205694075</v>
+        <v>7032235</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1678,22 +1555,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1708,31 +1575,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97363694</v>
+        <v>102947951</v>
       </c>
       <c r="B11" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,34 +1602,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grundflyberget, Jmt</t>
+          <t>Ammerån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528632.1654833439</v>
+        <v>527773</v>
       </c>
       <c r="R11" t="n">
-        <v>7032309.350764355</v>
+        <v>7032279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,22 +1656,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,53 +1676,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97363706</v>
+        <v>412661</v>
       </c>
       <c r="B12" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>248955</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,13 +1723,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527982.9049959956</v>
+        <v>527772</v>
       </c>
       <c r="R12" t="n">
-        <v>7032338.094098906</v>
+        <v>7032228</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1753,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,31 +1773,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97363686</v>
+        <v>97363732</v>
       </c>
       <c r="B13" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528057.7103785521</v>
+        <v>528092</v>
       </c>
       <c r="R13" t="n">
-        <v>7032297.989249053</v>
+        <v>7032586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,19 +1857,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,37 +1890,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97363696</v>
+        <v>97363671</v>
       </c>
       <c r="B14" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2389</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2112,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528631.2324305989</v>
+        <v>528126</v>
       </c>
       <c r="R14" t="n">
-        <v>7032313.373661366</v>
+        <v>7032614</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,21 +1958,11 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2168,6 +1971,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stock i glup</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2188,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97363710</v>
+        <v>486941</v>
       </c>
       <c r="B15" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,21 +2007,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3624</v>
+        <v>2412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2228,13 +2031,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527863.2346462847</v>
+        <v>527817</v>
       </c>
       <c r="R15" t="n">
-        <v>7032328.539061921</v>
+        <v>7032328</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,22 +2061,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,55 +2081,46 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97363678</v>
+        <v>97363710</v>
       </c>
       <c r="B16" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>3624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2344,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528633.0183511152</v>
+        <v>527863</v>
       </c>
       <c r="R16" t="n">
-        <v>7032314.285480627</v>
+        <v>7032329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,19 +2161,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,37 +2194,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97363720</v>
+        <v>97363656</v>
       </c>
       <c r="B17" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>3739</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527814.3344784513</v>
+        <v>527965</v>
       </c>
       <c r="R17" t="n">
-        <v>7032329.905101998</v>
+        <v>7032600</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,19 +2262,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,15 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97363714</v>
+        <v>97363717</v>
       </c>
       <c r="B18" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,21 +2306,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>3739</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2576,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527903.8993680176</v>
+        <v>527985</v>
       </c>
       <c r="R18" t="n">
-        <v>7032499.991420262</v>
+        <v>7032339</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,19 +2363,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,15 +2396,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97363733</v>
+        <v>97363651</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,21 +2407,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2692,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527848.5205145009</v>
+        <v>528774</v>
       </c>
       <c r="R19" t="n">
-        <v>7032318.556837915</v>
+        <v>7032315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,19 +2464,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,53 +2497,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97363718</v>
+        <v>102181442</v>
       </c>
       <c r="B20" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grundflyberget, Jmt</t>
+          <t>Ragunda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527859.3533848888</v>
+        <v>528062</v>
       </c>
       <c r="R20" t="n">
-        <v>7032619.634863658</v>
+        <v>7032322</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2838,22 +2563,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,53 +2583,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
-        </is>
-      </c>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97363737</v>
+        <v>97363722</v>
       </c>
       <c r="B21" t="n">
-        <v>85177</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>445</v>
+        <v>4379</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2924,10 +2630,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527973.0031582272</v>
+        <v>527980</v>
       </c>
       <c r="R21" t="n">
-        <v>7032342.038682798</v>
+        <v>7032341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,19 +2663,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,37 +2696,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97363685</v>
+        <v>97363720</v>
       </c>
       <c r="B22" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>248955</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3040,10 +2731,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528152.7322468611</v>
+        <v>527814</v>
       </c>
       <c r="R22" t="n">
-        <v>7032203.416449406</v>
+        <v>7032330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3073,19 +2764,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,37 +2797,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>97363666</v>
+        <v>1867084</v>
       </c>
       <c r="B23" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3156,13 +2832,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528056.3570609721</v>
+        <v>527775</v>
       </c>
       <c r="R23" t="n">
-        <v>7032298.873211677</v>
+        <v>7032330</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3186,22 +2862,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3216,53 +2882,48 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>97363725</v>
+        <v>97363733</v>
       </c>
       <c r="B24" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3272,10 +2933,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527797.8426897764</v>
+        <v>527848</v>
       </c>
       <c r="R24" t="n">
-        <v>7032369.625625329</v>
+        <v>7032319</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,19 +2966,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,35 +2999,34 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97363630</v>
+        <v>97363739</v>
       </c>
       <c r="B25" t="n">
-        <v>85156</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>436</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blekspindling agg.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius caesiostramineus s. lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3384,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527971.1935690971</v>
+        <v>527888</v>
       </c>
       <c r="R25" t="n">
-        <v>7032343.814498672</v>
+        <v>7032515</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3417,21 +3067,11 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3440,6 +3080,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3460,37 +3105,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97363740</v>
+        <v>1979994</v>
       </c>
       <c r="B26" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>248955</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3500,13 +3140,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527893.4470123298</v>
+        <v>527750</v>
       </c>
       <c r="R26" t="n">
-        <v>7032309.990029035</v>
+        <v>7032272</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3530,22 +3170,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,67 +3190,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Åsa Stenman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102181442</v>
+        <v>1979995</v>
       </c>
       <c r="B27" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ragunda, Jmt</t>
+          <t>Grundflyberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528062.431541526</v>
+        <v>527820</v>
       </c>
       <c r="R27" t="n">
-        <v>7032322.218084873</v>
+        <v>7032259</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3647,22 +3271,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,27 +3291,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102947951</v>
+        <v>97363714</v>
       </c>
       <c r="B28" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3705,34 +3318,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ammerån, Jmt</t>
+          <t>Grundflyberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527773.0689641597</v>
+        <v>527904</v>
       </c>
       <c r="R28" t="n">
-        <v>7032278.484190322</v>
+        <v>7032500</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,22 +3372,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,49 +3392,48 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97363705</v>
+        <v>97363666</v>
       </c>
       <c r="B29" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>504</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3841,10 +3443,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528075.3307644126</v>
+        <v>528056</v>
       </c>
       <c r="R29" t="n">
-        <v>7032232.299407193</v>
+        <v>7032299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3874,19 +3476,9 @@
           <t>2021-09-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,6 +3502,1622 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>97363696</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>528631</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7032313</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>97363707</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>528091</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7032592</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>97363721</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>528093</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7032584</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>97363694</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>528633</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7032309</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>97363736</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>528079</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7032608</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>97363734</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>528032</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7032609</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>97363718</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>527860</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7032619</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>97363678</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>528633</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7032314</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>97363686</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>528057</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7032298</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>97363725</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>527797</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7032370</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6476800</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>527819</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7032261</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2012-07-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2012-07-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>97363685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>528153</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7032203</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>97363706</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>527983</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7032338</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>97363715</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>527972</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7032602</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>97363740</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>527893</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7032310</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>97363741</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87291</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>248955</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tvillingspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius metarius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grundflyberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>528078</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7032606</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>

--- a/artfynd/A 62949-2021 artfynd.xlsx
+++ b/artfynd/A 62949-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363737</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62326102</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1487,6 +1527,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/206855</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/206856</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102947951</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/412661</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363732</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363671</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/486941</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363710</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363656</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363717</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2494,6 +2584,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363651</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2592,6 +2687,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102181442</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363722</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363720</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1867084</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363733</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3102,6 +3222,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363739</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1979994</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3304,6 +3434,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1979995</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3405,6 +3540,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363714</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3506,6 +3646,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363666</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3607,6 +3752,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363696</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3708,6 +3858,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363707</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3809,6 +3964,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363721</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3910,6 +4070,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363694</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4011,6 +4176,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363736</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4112,6 +4282,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363734</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4213,6 +4388,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363718</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4314,6 +4494,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363678</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4415,6 +4600,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363686</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4516,6 +4706,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363725</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4617,6 +4812,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6476800</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4718,6 +4918,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363685</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4819,6 +5024,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363706</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4920,6 +5130,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363715</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5021,6 +5236,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363740</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5122,8 +5342,59 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97363741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>